--- a/individual_voting_form.xlsx
+++ b/individual_voting_form.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktop\SurveyCTO_Voting_EVM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CCEA76-A400-4F28-A7D9-6D338008287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DBB5AA-D627-486B-A9E1-02EB2C1D827F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="561">
   <si>
     <t>type</t>
   </si>
@@ -642,18 +642,6 @@
   </si>
   <si>
     <t>aap.png</t>
-  </si>
-  <si>
-    <t>tmc</t>
-  </si>
-  <si>
-    <t>TMC (All India Trinamool Congress)</t>
-  </si>
-  <si>
-    <t>टीएमसी (अखिल भारतीय तृणमूल कांग्रेस)</t>
-  </si>
-  <si>
-    <t>tmc.png</t>
   </si>
   <si>
     <t>bsp</t>
@@ -1759,6 +1747,18 @@
   </si>
   <si>
     <t>वर्तमान जीपीएस निर्देशांक कैप्चर करें.</t>
+  </si>
+  <si>
+    <t>sp</t>
+  </si>
+  <si>
+    <t>sp.png</t>
+  </si>
+  <si>
+    <t>SP (Samajwadi Party)</t>
+  </si>
+  <si>
+    <t>एसपी (समाजवादी पार्टी)</t>
   </si>
 </sst>
 </file>
@@ -2388,6 +2388,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2430,324 +2431,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="159">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDBE5F1"/>
-          <bgColor rgb="FFDBE5F1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF99BCE7"/>
-          <bgColor rgb="FF99BCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92CDDC"/>
-          <bgColor rgb="FF92CDDC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBD4B4"/>
-          <bgColor rgb="FFFBD4B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBA005D"/>
-          <bgColor rgb="FFBA005D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAEB74"/>
-          <bgColor rgb="FFEAEB74"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7D480"/>
-          <bgColor rgb="FFE7D480"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDDE8C6"/>
-          <bgColor rgb="FFDDE8C6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE3E0CF"/>
-          <bgColor rgb="FFE3E0CF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFBB57"/>
-          <bgColor rgb="FFFFBB57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCC0D9"/>
-          <bgColor rgb="FFCCC0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2DBDA"/>
-          <bgColor rgb="FFF2DBDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAF1DD"/>
-          <bgColor rgb="FFEAF1DD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFD44B"/>
-          <bgColor rgb="FFFFD44B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD8D8D8"/>
-          <bgColor rgb="FFD8D8D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBFB00"/>
-          <bgColor rgb="FFFBFB00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF6969"/>
-          <bgColor rgb="FFFF6969"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEEB400"/>
-          <bgColor rgb="FFEEB400"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEEB400"/>
-          <bgColor rgb="FFEEB400"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF9900"/>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBBBB59"/>
-          <bgColor rgb="FFBBBB59"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9E004F"/>
-          <bgColor rgb="FF9E004F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE1AAA9"/>
-          <bgColor rgb="FFE1AAA9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB2A1C7"/>
-          <bgColor rgb="FFB2A1C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4E300"/>
-          <bgColor rgb="FFE4E300"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDCC97A"/>
-          <bgColor rgb="FFDCC97A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC2D69B"/>
-          <bgColor rgb="FFC2D69B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC4BD97"/>
-          <bgColor rgb="FFC4BD97"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF6D9E"/>
-          <bgColor rgb="FFFF6D9E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD6E3BC"/>
-          <bgColor rgb="FFD6E3BC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF4685D2"/>
-          <bgColor rgb="FF4685D2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB8CCE4"/>
-          <bgColor rgb="FFB8CCE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFABF8F"/>
-          <bgColor rgb="FFFABF8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF9900"/>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="127">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3207,8 +2895,16 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFBFB00"/>
-          <bgColor rgb="FFFBFB00"/>
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8D8D8"/>
+          <bgColor rgb="FFD8D8D8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3223,8 +2919,32 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFBFB00"/>
+          <bgColor rgb="FFFBFB00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFF6969"/>
           <bgColor rgb="FFFF6969"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8D8D8"/>
+          <bgColor rgb="FFD8D8D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3399,144 +3119,168 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF99BCE7"/>
-          <bgColor rgb="FF99BCE7"/>
+          <fgColor rgb="FFEEB400"/>
+          <bgColor rgb="FFEEB400"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDBE5F1"/>
-          <bgColor rgb="FFDBE5F1"/>
+          <fgColor rgb="FFEEB400"/>
+          <bgColor rgb="FFEEB400"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFBD4B4"/>
-          <bgColor rgb="FFFBD4B4"/>
+          <fgColor rgb="FFFF9900"/>
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF92CDDC"/>
-          <bgColor rgb="FF92CDDC"/>
+          <fgColor rgb="FFFF9900"/>
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFBA005D"/>
-          <bgColor rgb="FFBA005D"/>
+          <fgColor rgb="FFFABF8F"/>
+          <bgColor rgb="FFFABF8F"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE3E0CF"/>
-          <bgColor rgb="FFE3E0CF"/>
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDDE8C6"/>
-          <bgColor rgb="FFDDE8C6"/>
+          <fgColor rgb="FF4685D2"/>
+          <bgColor rgb="FF4685D2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE7D480"/>
-          <bgColor rgb="FFE7D480"/>
+          <fgColor rgb="FFD6E3BC"/>
+          <bgColor rgb="FFD6E3BC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEAEB74"/>
-          <bgColor rgb="FFEAEB74"/>
+          <fgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFBB57"/>
-          <bgColor rgb="FFFFBB57"/>
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF2DBDA"/>
-          <bgColor rgb="FFF2DBDA"/>
+          <fgColor rgb="FFC4BD97"/>
+          <bgColor rgb="FFC4BD97"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFCCC0D9"/>
-          <bgColor rgb="FFCCC0D9"/>
+          <fgColor rgb="FFC2D69B"/>
+          <bgColor rgb="FFC2D69B"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEAF1DD"/>
-          <bgColor rgb="FFEAF1DD"/>
+          <fgColor rgb="FFDCC97A"/>
+          <bgColor rgb="FFDCC97A"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFD44B"/>
-          <bgColor rgb="FFFFD44B"/>
+          <fgColor rgb="FFE4E300"/>
+          <bgColor rgb="FFE4E300"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD8D8D8"/>
-          <bgColor rgb="FFD8D8D8"/>
+          <fgColor rgb="FFB2A1C7"/>
+          <bgColor rgb="FFB2A1C7"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFBFB00"/>
-          <bgColor rgb="FFFBFB00"/>
+          <fgColor rgb="FFE1AAA9"/>
+          <bgColor rgb="FFE1AAA9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
+          <fgColor rgb="FF9E004F"/>
+          <bgColor rgb="FF9E004F"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFF6969"/>
-          <bgColor rgb="FFFF6969"/>
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF6D9E"/>
+          <bgColor rgb="FFFF6D9E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBBBB59"/>
+          <bgColor rgb="FFBBBB59"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3919,7 +3663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1002"/>
+  <dimension ref="A1:Z1001"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -4091,10 +3835,19 @@
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4102,13 +3855,13 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N10" t="s">
         <v>44</v>
@@ -4116,16 +3869,25 @@
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="I11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" t="s">
+        <v>552</v>
       </c>
       <c r="N11" t="s">
         <v>44</v>
@@ -4133,25 +3895,16 @@
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" t="s">
-        <v>556</v>
+        <v>57</v>
       </c>
       <c r="N12" t="s">
         <v>44</v>
@@ -4159,73 +3912,73 @@
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N13" t="s">
         <v>44</v>
       </c>
+      <c r="V13" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="N14" t="s">
         <v>44</v>
       </c>
       <c r="V14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N15" t="s">
         <v>44</v>
       </c>
-      <c r="V15" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N16" t="s">
         <v>44</v>
@@ -4233,135 +3986,119 @@
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>78</v>
+      </c>
+      <c r="L17" t="s">
+        <v>79</v>
       </c>
       <c r="N17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="L18" t="s">
-        <v>79</v>
-      </c>
-      <c r="N18" t="s">
+    <row r="18" spans="1:14" s="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>550</v>
+      </c>
+      <c r="C18" s="60" t="s">
+        <v>551</v>
+      </c>
+      <c r="D18" s="60" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" t="s">
+        <v>554</v>
+      </c>
+      <c r="H19" t="s">
+        <v>85</v>
+      </c>
+      <c r="N19" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" s="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="80" t="s">
-        <v>554</v>
-      </c>
-      <c r="C19" s="80" t="s">
-        <v>555</v>
-      </c>
-      <c r="D19" s="80" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>558</v>
-      </c>
-      <c r="H20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>548</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>549</v>
+      </c>
+      <c r="D21" s="60" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" t="s">
+        <v>556</v>
+      </c>
+      <c r="N22" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>88</v>
-      </c>
-      <c r="N21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" s="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="80" t="s">
-        <v>552</v>
-      </c>
-      <c r="C22" s="80" t="s">
-        <v>553</v>
-      </c>
-      <c r="D22" s="80" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" t="s">
-        <v>560</v>
-      </c>
-      <c r="N23" t="s">
-        <v>44</v>
-      </c>
-    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5340,417 +5077,294 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <conditionalFormatting sqref="A1:W18 X11:Z15 A23:W1002 A20:W21">
-    <cfRule type="expression" dxfId="158" priority="95" stopIfTrue="1">
+  <conditionalFormatting sqref="X10:Z14 A1:W17">
+    <cfRule type="expression" dxfId="126" priority="95" stopIfTrue="1">
       <formula>$A1="file"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="96" stopIfTrue="1">
       <formula>$A1="enumerator"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="97" stopIfTrue="1">
       <formula>OR(AND(LEFT($A1, 14)="sensor_stream ", LEN($A1)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A1, 15)))), AND(LEFT($A1, 17)="sensor_statistic ", LEN($A1)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A1, 18)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="155" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="98" stopIfTrue="1">
       <formula>$A1="comments"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="99" stopIfTrue="1">
       <formula>OR($A1="audio", $A1="video")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="100" stopIfTrue="1">
       <formula>$A1="image"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="101" stopIfTrue="1">
       <formula>OR($A1="date", $A1="datetime", $A1="time")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="151" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="102" stopIfTrue="1">
       <formula>OR($A1="calculate", $A1="calculate_here")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="103" stopIfTrue="1">
       <formula>$A1="note"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="104" stopIfTrue="1">
       <formula>$A1="barcode"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="105" stopIfTrue="1">
       <formula>OR($A1="geopoint", $A1="geoshape", $A1="geotrace")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="147" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="106" stopIfTrue="1">
       <formula>OR($A1="audio audit", $A1="text audit", $A1="speed violations count", $A1="speed violations list", $A1="speed violations audit")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="107" stopIfTrue="1">
       <formula>OR($A1="username", $A1="phonenumber", $A1="start", $A1="end", $A1="deviceid", $A1="subscriberid", $A1="simserial", $A1="caseid")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="108" stopIfTrue="1">
       <formula>OR(AND(LEFT($A1, 16)="select_multiple ", LEN($A1)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A1, 17)))), AND(LEFT($A1, 11)="select_one ", LEN($A1)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A1, 12)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="109" stopIfTrue="1">
       <formula>$A1="decimal"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="143" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="110" stopIfTrue="1">
       <formula>$A1="integer"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="111" stopIfTrue="1">
       <formula>$A1="text"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="112" stopIfTrue="1">
       <formula>$A1="end repeat"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="113" stopIfTrue="1">
       <formula>$A1="begin repeat"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="139" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="114" stopIfTrue="1">
       <formula>$A1="end group"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="115" stopIfTrue="1">
       <formula>$A1="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B18 F1:F18 F23:F1002 B23:B1002 F20:F21 B20:B21">
-    <cfRule type="expression" dxfId="137" priority="86" stopIfTrue="1">
-      <formula>OR($A1="audio audit", $A1="text audit", $A1="speed violations count", $A1="speed violations list", $A1="speed violations audit")</formula>
+  <conditionalFormatting sqref="A19:W1001">
+    <cfRule type="expression" dxfId="105" priority="56" stopIfTrue="1">
+      <formula>$A19="file"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="57" stopIfTrue="1">
+      <formula>$A19="enumerator"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="58" stopIfTrue="1">
+      <formula>OR(AND(LEFT($A19, 14)="sensor_stream ", LEN($A19)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A19, 15)))), AND(LEFT($A19, 17)="sensor_statistic ", LEN($A19)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A19, 18)))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="59" stopIfTrue="1">
+      <formula>$A19="comments"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="60" stopIfTrue="1">
+      <formula>OR($A19="audio", $A19="video")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="61" stopIfTrue="1">
+      <formula>$A19="image"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="62" stopIfTrue="1">
+      <formula>OR($A19="date", $A19="datetime", $A19="time")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="63" stopIfTrue="1">
+      <formula>OR($A19="calculate", $A19="calculate_here")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="64" stopIfTrue="1">
+      <formula>$A19="note"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="65" stopIfTrue="1">
+      <formula>$A19="barcode"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="95" priority="66" stopIfTrue="1">
+      <formula>OR($A19="geopoint", $A19="geoshape", $A19="geotrace")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="67" stopIfTrue="1">
+      <formula>OR($A19="audio audit", $A19="text audit", $A19="speed violations count", $A19="speed violations list", $A19="speed violations audit")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="68" stopIfTrue="1">
+      <formula>OR($A19="username", $A19="phonenumber", $A19="start", $A19="end", $A19="deviceid", $A19="subscriberid", $A19="simserial", $A19="caseid")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="69" stopIfTrue="1">
+      <formula>OR(AND(LEFT($A19, 16)="select_multiple ", LEN($A19)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A19, 17)))), AND(LEFT($A19, 11)="select_one ", LEN($A19)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A19, 12)))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="70" stopIfTrue="1">
+      <formula>$A19="decimal"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="71" stopIfTrue="1">
+      <formula>$A19="integer"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="72" stopIfTrue="1">
+      <formula>$A19="text"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="73" stopIfTrue="1">
+      <formula>$A19="end repeat"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="87" priority="74" stopIfTrue="1">
+      <formula>$A19="begin repeat"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="75" stopIfTrue="1">
+      <formula>$A19="end group"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="76" stopIfTrue="1">
+      <formula>$A19="begin group"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:Z18">
+    <cfRule type="expression" dxfId="84" priority="17" stopIfTrue="1">
+      <formula>$A18="file"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="18" stopIfTrue="1">
+      <formula>$A18="enumerator"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="19" stopIfTrue="1">
+      <formula>OR(AND(LEFT($A18, 14)="sensor_stream ", LEN($A18)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A18, 15)))), AND(LEFT($A18, 17)="sensor_statistic ", LEN($A18)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A18, 18)))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="20" stopIfTrue="1">
+      <formula>$A18="comments"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="21" stopIfTrue="1">
+      <formula>OR($A18="audio", $A18="video")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="22" stopIfTrue="1">
+      <formula>$A18="image"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="23" stopIfTrue="1">
+      <formula>OR($A18="date", $A18="datetime", $A18="time")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="24" stopIfTrue="1">
+      <formula>OR($A18="calculate", $A18="calculate_here")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="25" stopIfTrue="1">
+      <formula>$A18="note"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="26" stopIfTrue="1">
+      <formula>$A18="barcode"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="27" stopIfTrue="1">
+      <formula>OR($A18="geopoint", $A18="geoshape", $A18="geotrace")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="28" stopIfTrue="1">
+      <formula>OR($A18="audio audit", $A18="text audit", $A18="speed violations count", $A18="speed violations list", $A18="speed violations audit")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="29" stopIfTrue="1">
+      <formula>OR($A18="username", $A18="phonenumber", $A18="start", $A18="end", $A18="deviceid", $A18="subscriberid", $A18="simserial", $A18="caseid")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="30" stopIfTrue="1">
+      <formula>OR(AND(LEFT($A18, 16)="select_multiple ", LEN($A18)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A18, 17)))), AND(LEFT($A18, 11)="select_one ", LEN($A18)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A18, 12)))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="31" stopIfTrue="1">
+      <formula>$A18="decimal"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="32" stopIfTrue="1">
+      <formula>$A18="integer"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="33" stopIfTrue="1">
+      <formula>$A18="text"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="34" stopIfTrue="1">
+      <formula>$A18="end repeat"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="35" stopIfTrue="1">
+      <formula>$A18="begin repeat"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="36" stopIfTrue="1">
+      <formula>$A18="end group"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="37" stopIfTrue="1">
+      <formula>$A18="begin group"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B17 F1:F17">
+    <cfRule type="expression" dxfId="63" priority="117" stopIfTrue="1">
       <formula>OR(AND(LEFT($A1, 14)="sensor_stream ", LEN($A1)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A1, 15)))), AND(LEFT($A1, 17)="sensor_statistic ", LEN($A1)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A1, 18)))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B18 N1:N18 N23:N1002 B23:B1002 N20:N21 B20:B21">
-    <cfRule type="expression" dxfId="135" priority="91" stopIfTrue="1">
+  <conditionalFormatting sqref="B1:B17">
+    <cfRule type="expression" dxfId="62" priority="116" stopIfTrue="1">
+      <formula>$A1="comments"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1001 F1:F1001">
+    <cfRule type="expression" dxfId="61" priority="8" stopIfTrue="1">
+      <formula>OR($A1="audio audit", $A1="text audit", $A1="speed violations count", $A1="speed violations list", $A1="speed violations audit")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1001 N1:N1001">
+    <cfRule type="expression" dxfId="60" priority="13" stopIfTrue="1">
       <formula>OR($A1="calculate", $A1="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B18 B23:B1002 B20:B21">
-    <cfRule type="expression" dxfId="134" priority="116" stopIfTrue="1">
-      <formula>$A1="comments"</formula>
+  <conditionalFormatting sqref="B18 F18">
+    <cfRule type="expression" dxfId="59" priority="39" stopIfTrue="1">
+      <formula>OR(AND(LEFT($A18, 14)="sensor_stream ", LEN($A18)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A18, 15)))), AND(LEFT($A18, 17)="sensor_statistic ", LEN($A18)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A18, 18)))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C18 F1:F18 I1:I18 I23:I1002 F23:F1002 B23:C1002 I20:I21 F20:F21 B20:C21">
-    <cfRule type="expression" dxfId="133" priority="79" stopIfTrue="1">
+  <conditionalFormatting sqref="B18">
+    <cfRule type="expression" dxfId="58" priority="38" stopIfTrue="1">
+      <formula>$A18="comments"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B1001 F19:F1001">
+    <cfRule type="expression" dxfId="57" priority="78" stopIfTrue="1">
+      <formula>OR(AND(LEFT($A19, 14)="sensor_stream ", LEN($A19)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A19, 15)))), AND(LEFT($A19, 17)="sensor_statistic ", LEN($A19)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A19, 18)))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B1001">
+    <cfRule type="expression" dxfId="56" priority="77" stopIfTrue="1">
+      <formula>$A19="comments"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:C1001 F1:F1001 I1:I1001">
+    <cfRule type="expression" dxfId="55" priority="1" stopIfTrue="1">
       <formula>$A1="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C18 F1:F18 F23:F1002 B23:C1002 F20:F21 B20:C21">
-    <cfRule type="expression" dxfId="132" priority="85" stopIfTrue="1">
+  <conditionalFormatting sqref="B1:C1001 F1:F1001">
+    <cfRule type="expression" dxfId="54" priority="7" stopIfTrue="1">
       <formula>OR(AND(LEFT($A1, 16)="select_multiple ", LEN($A1)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A1, 17)))), AND(LEFT($A1, 11)="select_one ", LEN($A1)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A1, 12)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="131" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="14" stopIfTrue="1">
       <formula>OR($A1="date", $A1="datetime", $A1="time")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="15" stopIfTrue="1">
       <formula>$A1="image"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C18 I1:I18 O1:O18 O23:O1002 I23:I1002 B23:C1002 O20:O21 I20:I21 B20:C21">
-    <cfRule type="expression" dxfId="129" priority="80" stopIfTrue="1">
+  <conditionalFormatting sqref="B1:C1001 I1:I1001 O1:O1001">
+    <cfRule type="expression" dxfId="51" priority="2" stopIfTrue="1">
       <formula>$A1="begin repeat"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C18 B23:C1002 B20:C21">
-    <cfRule type="expression" dxfId="128" priority="87" stopIfTrue="1">
+  <conditionalFormatting sqref="B1:C1001">
+    <cfRule type="expression" dxfId="50" priority="9" stopIfTrue="1">
       <formula>$A1="file"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="10" stopIfTrue="1">
       <formula>$A1="note"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="11" stopIfTrue="1">
       <formula>$A1="barcode"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="12" stopIfTrue="1">
       <formula>OR($A1="geopoint", $A1="geoshape", $A1="geotrace")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="16" stopIfTrue="1">
       <formula>OR($A1="audio", $A1="video")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D18 F1:F18 F23:F1002 B23:D1002 F20:F21 B20:D21">
-    <cfRule type="expression" dxfId="123" priority="81" stopIfTrue="1">
+  <conditionalFormatting sqref="B1:D1001 F1:F1001">
+    <cfRule type="expression" dxfId="45" priority="3" stopIfTrue="1">
       <formula>$A1="enumerator"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="4" stopIfTrue="1">
       <formula>$A1="text"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D18 G1:H18 G23:H1002 B23:D1002 G20:H21 B20:D21">
-    <cfRule type="expression" dxfId="121" priority="83" stopIfTrue="1">
+  <conditionalFormatting sqref="B1:D1001 G1:H1001">
+    <cfRule type="expression" dxfId="43" priority="5" stopIfTrue="1">
       <formula>$A1="integer"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="6" stopIfTrue="1">
       <formula>$A1="decimal"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22:W22">
-    <cfRule type="expression" dxfId="119" priority="56" stopIfTrue="1">
-      <formula>$A22="file"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="118" priority="57" stopIfTrue="1">
-      <formula>$A22="enumerator"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="117" priority="58" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A22, 14)="sensor_stream ", LEN($A22)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A22, 15)))), AND(LEFT($A22, 17)="sensor_statistic ", LEN($A22)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A22, 18)))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="116" priority="59" stopIfTrue="1">
-      <formula>$A22="comments"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="115" priority="60" stopIfTrue="1">
-      <formula>OR($A22="audio", $A22="video")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="114" priority="61" stopIfTrue="1">
-      <formula>$A22="image"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="62" stopIfTrue="1">
-      <formula>OR($A22="date", $A22="datetime", $A22="time")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="112" priority="63" stopIfTrue="1">
-      <formula>OR($A22="calculate", $A22="calculate_here")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="111" priority="64" stopIfTrue="1">
-      <formula>$A22="note"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="110" priority="65" stopIfTrue="1">
-      <formula>$A22="barcode"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="66" stopIfTrue="1">
-      <formula>OR($A22="geopoint", $A22="geoshape", $A22="geotrace")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="108" priority="67" stopIfTrue="1">
-      <formula>OR($A22="audio audit", $A22="text audit", $A22="speed violations count", $A22="speed violations list", $A22="speed violations audit")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="107" priority="68" stopIfTrue="1">
-      <formula>OR($A22="username", $A22="phonenumber", $A22="start", $A22="end", $A22="deviceid", $A22="subscriberid", $A22="simserial", $A22="caseid")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="106" priority="69" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A22, 16)="select_multiple ", LEN($A22)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A22, 17)))), AND(LEFT($A22, 11)="select_one ", LEN($A22)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A22, 12)))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="70" stopIfTrue="1">
-      <formula>$A22="decimal"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="71" stopIfTrue="1">
-      <formula>$A22="integer"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="72" stopIfTrue="1">
-      <formula>$A22="text"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="73" stopIfTrue="1">
-      <formula>$A22="end repeat"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="74" stopIfTrue="1">
-      <formula>$A22="begin repeat"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="75" stopIfTrue="1">
-      <formula>$A22="end group"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="76" stopIfTrue="1">
-      <formula>$A22="begin group"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22 F22">
-    <cfRule type="expression" dxfId="98" priority="47" stopIfTrue="1">
-      <formula>OR($A22="audio audit", $A22="text audit", $A22="speed violations count", $A22="speed violations list", $A22="speed violations audit")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="78" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A22, 14)="sensor_stream ", LEN($A22)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A22, 15)))), AND(LEFT($A22, 17)="sensor_statistic ", LEN($A22)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A22, 18)))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22 N22">
-    <cfRule type="expression" dxfId="96" priority="52" stopIfTrue="1">
-      <formula>OR($A22="calculate", $A22="calculate_here")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="expression" dxfId="95" priority="77" stopIfTrue="1">
-      <formula>$A22="comments"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:C22 F22 I22">
-    <cfRule type="expression" dxfId="94" priority="40" stopIfTrue="1">
-      <formula>$A22="begin group"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:C22 F22">
-    <cfRule type="expression" dxfId="93" priority="46" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A22, 16)="select_multiple ", LEN($A22)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A22, 17)))), AND(LEFT($A22, 11)="select_one ", LEN($A22)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A22, 12)))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="92" priority="53" stopIfTrue="1">
-      <formula>OR($A22="date", $A22="datetime", $A22="time")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="54" stopIfTrue="1">
-      <formula>$A22="image"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:C22 I22 O22">
-    <cfRule type="expression" dxfId="90" priority="41" stopIfTrue="1">
-      <formula>$A22="begin repeat"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:C22">
-    <cfRule type="expression" dxfId="89" priority="48" stopIfTrue="1">
-      <formula>$A22="file"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="49" stopIfTrue="1">
-      <formula>$A22="note"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="50" stopIfTrue="1">
-      <formula>$A22="barcode"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="51" stopIfTrue="1">
-      <formula>OR($A22="geopoint", $A22="geoshape", $A22="geotrace")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="55" stopIfTrue="1">
-      <formula>OR($A22="audio", $A22="video")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:D22 F22">
-    <cfRule type="expression" dxfId="84" priority="42" stopIfTrue="1">
-      <formula>$A22="enumerator"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="43" stopIfTrue="1">
-      <formula>$A22="text"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:D22 G22:H22">
-    <cfRule type="expression" dxfId="82" priority="44" stopIfTrue="1">
-      <formula>$A22="integer"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="45" stopIfTrue="1">
-      <formula>$A22="decimal"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:Z19">
-    <cfRule type="expression" dxfId="22" priority="17" stopIfTrue="1">
-      <formula>$A19="file"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="18" stopIfTrue="1">
-      <formula>$A19="enumerator"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="19" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A19, 14)="sensor_stream ", LEN($A19)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A19, 15)))), AND(LEFT($A19, 17)="sensor_statistic ", LEN($A19)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A19, 18)))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="20" stopIfTrue="1">
-      <formula>$A19="comments"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
-      <formula>OR($A19="audio", $A19="video")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="22" stopIfTrue="1">
-      <formula>$A19="image"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="23" stopIfTrue="1">
-      <formula>OR($A19="date", $A19="datetime", $A19="time")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="24" stopIfTrue="1">
-      <formula>OR($A19="calculate", $A19="calculate_here")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
-      <formula>$A19="note"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="26" stopIfTrue="1">
-      <formula>$A19="barcode"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="27" stopIfTrue="1">
-      <formula>OR($A19="geopoint", $A19="geoshape", $A19="geotrace")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="28" stopIfTrue="1">
-      <formula>OR($A19="audio audit", $A19="text audit", $A19="speed violations count", $A19="speed violations list", $A19="speed violations audit")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="29" stopIfTrue="1">
-      <formula>OR($A19="username", $A19="phonenumber", $A19="start", $A19="end", $A19="deviceid", $A19="subscriberid", $A19="simserial", $A19="caseid")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="30" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A19, 16)="select_multiple ", LEN($A19)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A19, 17)))), AND(LEFT($A19, 11)="select_one ", LEN($A19)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A19, 12)))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="31" stopIfTrue="1">
-      <formula>$A19="decimal"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="32" stopIfTrue="1">
-      <formula>$A19="integer"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="33" stopIfTrue="1">
-      <formula>$A19="text"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="34" stopIfTrue="1">
-      <formula>$A19="end repeat"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="35" stopIfTrue="1">
-      <formula>$A19="begin repeat"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="36" stopIfTrue="1">
-      <formula>$A19="end group"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="37" stopIfTrue="1">
-      <formula>$A19="begin group"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19 F19">
-    <cfRule type="expression" dxfId="16" priority="8" stopIfTrue="1">
-      <formula>OR($A19="audio audit", $A19="text audit", $A19="speed violations count", $A19="speed violations list", $A19="speed violations audit")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="39" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A19, 14)="sensor_stream ", LEN($A19)&gt;14, NOT(ISNUMBER(SEARCH(" ", $A19, 15)))), AND(LEFT($A19, 17)="sensor_statistic ", LEN($A19)&gt;17, NOT(ISNUMBER(SEARCH(" ", $A19, 18)))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19 N19">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
-      <formula>OR($A19="calculate", $A19="calculate_here")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
-    <cfRule type="expression" dxfId="14" priority="38" stopIfTrue="1">
-      <formula>$A19="comments"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:C19 F19 I19">
-    <cfRule type="expression" dxfId="13" priority="1" stopIfTrue="1">
-      <formula>$A19="begin group"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:C19 F19">
-    <cfRule type="expression" dxfId="12" priority="7" stopIfTrue="1">
-      <formula>OR(AND(LEFT($A19, 16)="select_multiple ", LEN($A19)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A19, 17)))), AND(LEFT($A19, 11)="select_one ", LEN($A19)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A19, 12)))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="14" stopIfTrue="1">
-      <formula>OR($A19="date", $A19="datetime", $A19="time")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="15" stopIfTrue="1">
-      <formula>$A19="image"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:C19 I19 O19">
-    <cfRule type="expression" dxfId="9" priority="2" stopIfTrue="1">
-      <formula>$A19="begin repeat"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:C19">
-    <cfRule type="expression" dxfId="5" priority="9" stopIfTrue="1">
-      <formula>$A19="file"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="10" stopIfTrue="1">
-      <formula>$A19="note"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="11" stopIfTrue="1">
-      <formula>$A19="barcode"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
-      <formula>OR($A19="geopoint", $A19="geoshape", $A19="geotrace")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="16" stopIfTrue="1">
-      <formula>OR($A19="audio", $A19="video")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:D19 F19">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>$A19="enumerator"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
-      <formula>$A19="text"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:D19 G19:H19">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
-      <formula>$A19="integer"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
-      <formula>$A19="decimal"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.74791666666666667" right="0.74791666666666667" top="0.98402777777777772" bottom="0.98402777777777772" header="0" footer="0"/>
@@ -6361,16 +5975,16 @@
         <v>189</v>
       </c>
       <c r="B38" t="s">
-        <v>202</v>
+        <v>557</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>559</v>
       </c>
       <c r="D38" t="s">
-        <v>204</v>
+        <v>560</v>
       </c>
       <c r="E38" t="s">
-        <v>205</v>
+        <v>558</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6378,16 +5992,16 @@
         <v>189</v>
       </c>
       <c r="B39" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C39" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6395,16 +6009,16 @@
         <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C40" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D40" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E40" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6412,16 +6026,16 @@
         <v>189</v>
       </c>
       <c r="B41" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C41" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D41" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E41" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6429,13 +6043,13 @@
         <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D42" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F42" t="s">
         <v>105</v>
@@ -6446,13 +6060,13 @@
         <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C43" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D43" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F43" t="s">
         <v>108</v>
@@ -6463,13 +6077,13 @@
         <v>114</v>
       </c>
       <c r="B44" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C44" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D44" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F44" t="s">
         <v>111</v>
@@ -6480,16 +6094,16 @@
         <v>133</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C45" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F45" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6497,16 +6111,16 @@
         <v>133</v>
       </c>
       <c r="B46" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D46" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F46" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6514,16 +6128,16 @@
         <v>133</v>
       </c>
       <c r="B47" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D47" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F47" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6531,16 +6145,16 @@
         <v>133</v>
       </c>
       <c r="B48" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D48" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F48" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6548,16 +6162,16 @@
         <v>133</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C49" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F49" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6565,16 +6179,16 @@
         <v>133</v>
       </c>
       <c r="B50" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C50" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D50" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F50" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -7529,7 +7143,7 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.74791666666666667" right="0.74791666666666667" top="0.98402777777777772" bottom="0.98402777777777772" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7548,22 +7162,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="7"/>
@@ -7588,19 +7202,19 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C2" s="5" t="str">
         <f ca="1">TEXT(YEAR(NOW())-2000, "00") &amp; TEXT(MONTH(NOW()), "00") &amp; TEXT(DAY(NOW()), "00") &amp; TEXT(HOUR(NOW()), "00") &amp; TEXT(MINUTE(NOW()), "00")</f>
-        <v>2607082137</v>
+        <v>2607082151</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="9"/>
       <c r="F2" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8617,10 +8231,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="70"/>
+      <c r="A1" s="70" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" s="71"/>
       <c r="C1" s="10"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -8652,8 +8266,8 @@
       <c r="AE1" s="2"/>
     </row>
     <row r="2" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
       <c r="C2" s="10"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -8685,10 +8299,10 @@
       <c r="AE2" s="2"/>
     </row>
     <row r="3" spans="1:31" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="71" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3" s="63"/>
+      <c r="A3" s="72" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="64"/>
       <c r="C3" s="10"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -8720,10 +8334,10 @@
       <c r="AE3" s="2"/>
     </row>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="60" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="61"/>
+      <c r="A4" s="61" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="62"/>
       <c r="C4" s="10"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -8795,16 +8409,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>6</v>
@@ -8816,10 +8430,10 @@
         <v>8</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>11</v>
@@ -8834,7 +8448,7 @@
         <v>14</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Q6" s="11" t="s">
         <v>15</v>
@@ -8855,13 +8469,13 @@
         <v>20</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="X6" s="11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="Y6" s="11" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Z6" s="11" t="s">
         <v>21</v>
@@ -8882,94 +8496,94 @@
     </row>
     <row r="7" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="F7" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="G7" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="H7" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="I7" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="J7" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="K7" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="L7" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="M7" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="N7" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="O7" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="P7" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="Q7" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="R7" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="O7" s="14" t="s">
+      <c r="S7" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="T7" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="Q7" s="14" t="s">
+      <c r="U7" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="R7" s="14" t="s">
+      <c r="V7" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="S7" s="14" t="s">
+      <c r="W7" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="T7" s="14" t="s">
+      <c r="X7" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="Y7" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="V7" s="14" t="s">
+      <c r="Z7" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="AA7" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="X7" s="14" t="s">
+      <c r="AB7" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="Y7" s="14" t="s">
+      <c r="AC7" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="Z7" s="16" t="s">
+      <c r="AD7" s="14" t="s">
         <v>284</v>
-      </c>
-      <c r="AA7" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="AB7" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="AC7" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="AD7" s="14" t="s">
-        <v>288</v>
       </c>
       <c r="AE7" s="17"/>
     </row>
@@ -8978,77 +8592,77 @@
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="H8" s="18"/>
       <c r="I8" s="20" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="20" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="M8" s="20" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="N8" s="20" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="P8" s="18"/>
       <c r="Q8" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="R8" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="S8" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="T8" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="U8" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="V8" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="W8" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="X8" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="Y8" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z8" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="R8" s="20" t="s">
+      <c r="AA8" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="S8" s="20" t="s">
+      <c r="AB8" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="AC8" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="T8" s="20" t="s">
+      <c r="AD8" s="20" t="s">
         <v>296</v>
-      </c>
-      <c r="U8" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="V8" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="W8" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="X8" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="Y8" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z8" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="AA8" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="AB8" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="AC8" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="AD8" s="20" t="s">
-        <v>300</v>
       </c>
       <c r="AE8" s="17"/>
     </row>
@@ -9086,10 +8700,10 @@
       <c r="AE9" s="2"/>
     </row>
     <row r="10" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="64" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="65"/>
+      <c r="A10" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="B10" s="66"/>
       <c r="C10" s="22"/>
       <c r="D10" s="23"/>
       <c r="E10" s="23"/>
@@ -9155,20 +8769,20 @@
     </row>
     <row r="12" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
       <c r="H12" s="26" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I12" s="26"/>
       <c r="J12" s="26"/>
@@ -9196,20 +8810,20 @@
     </row>
     <row r="13" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>302</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>306</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
       <c r="H13" s="27" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
@@ -9237,20 +8851,20 @@
     </row>
     <row r="14" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="26"/>
@@ -9278,20 +8892,20 @@
     </row>
     <row r="15" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
       <c r="H15" s="26" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
@@ -9322,10 +8936,10 @@
         <v>40</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="26"/>
@@ -9361,17 +8975,17 @@
         <v>40</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D17" s="26"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
       <c r="H17" s="26" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="26"/>
@@ -9402,10 +9016,10 @@
         <v>48</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="26"/>
@@ -9438,13 +9052,13 @@
     </row>
     <row r="19" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="26"/>
@@ -9477,13 +9091,13 @@
     </row>
     <row r="20" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="26"/>
@@ -9516,20 +9130,20 @@
     </row>
     <row r="21" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
       <c r="H21" s="26" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I21" s="26"/>
       <c r="J21" s="26"/>
@@ -9557,20 +9171,20 @@
     </row>
     <row r="22" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="C22" s="27" t="s">
         <v>317</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>321</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
       <c r="F22" s="26"/>
       <c r="G22" s="26"/>
       <c r="H22" s="26" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I22" s="26"/>
       <c r="J22" s="26"/>
@@ -9598,20 +9212,20 @@
     </row>
     <row r="23" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
       <c r="H23" s="26" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I23" s="26"/>
       <c r="J23" s="26"/>
@@ -9639,20 +9253,20 @@
     </row>
     <row r="24" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
       <c r="H24" s="26" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I24" s="26"/>
       <c r="J24" s="26"/>
@@ -9680,20 +9294,20 @@
     </row>
     <row r="25" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
       <c r="H25" s="26" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
@@ -9721,20 +9335,20 @@
     </row>
     <row r="26" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="26" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I26" s="26"/>
       <c r="J26" s="26"/>
@@ -9762,20 +9376,20 @@
     </row>
     <row r="27" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I27" s="26"/>
       <c r="J27" s="26"/>
@@ -9803,20 +9417,20 @@
     </row>
     <row r="28" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="26"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="I28" s="26"/>
       <c r="J28" s="26"/>
@@ -9844,20 +9458,20 @@
     </row>
     <row r="29" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="26"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
@@ -9885,20 +9499,20 @@
     </row>
     <row r="30" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D30" s="26"/>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
       <c r="H30" s="26" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
@@ -9926,20 +9540,20 @@
     </row>
     <row r="31" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
       <c r="H31" s="26" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
@@ -9967,20 +9581,20 @@
     </row>
     <row r="32" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
       <c r="H32" s="26" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
@@ -10008,20 +9622,20 @@
     </row>
     <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="26"/>
       <c r="G33" s="26"/>
       <c r="H33" s="26" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
@@ -10049,20 +9663,20 @@
     </row>
     <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="26"/>
       <c r="G34" s="26"/>
       <c r="H34" s="26" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
@@ -10090,13 +9704,13 @@
     </row>
     <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D35" s="25"/>
       <c r="E35" s="26"/>
@@ -10129,20 +9743,20 @@
     </row>
     <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="26"/>
       <c r="G36" s="26"/>
       <c r="H36" s="26" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
@@ -10170,20 +9784,20 @@
     </row>
     <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
       <c r="F37" s="26"/>
       <c r="G37" s="26"/>
       <c r="H37" s="26" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I37" s="26"/>
       <c r="J37" s="26"/>
@@ -10211,20 +9825,20 @@
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="C38" s="27" t="s">
         <v>347</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>351</v>
       </c>
       <c r="D38" s="26"/>
       <c r="E38" s="26"/>
       <c r="F38" s="26"/>
       <c r="G38" s="26"/>
       <c r="H38" s="26" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I38" s="26"/>
       <c r="J38" s="26"/>
@@ -10252,20 +9866,20 @@
     </row>
     <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D39" s="26"/>
       <c r="E39" s="26"/>
       <c r="F39" s="26"/>
       <c r="G39" s="26"/>
       <c r="H39" s="26" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I39" s="26"/>
       <c r="J39" s="26"/>
@@ -10293,20 +9907,20 @@
     </row>
     <row r="40" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D40" s="26"/>
       <c r="E40" s="26"/>
       <c r="F40" s="26"/>
       <c r="G40" s="26"/>
       <c r="H40" s="26" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I40" s="26"/>
       <c r="J40" s="26"/>
@@ -10334,20 +9948,20 @@
     </row>
     <row r="41" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="26"/>
       <c r="F41" s="26"/>
       <c r="G41" s="26"/>
       <c r="H41" s="26" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I41" s="26"/>
       <c r="J41" s="26"/>
@@ -10375,20 +9989,20 @@
     </row>
     <row r="42" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D42" s="26"/>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
       <c r="G42" s="26"/>
       <c r="H42" s="26" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I42" s="26"/>
       <c r="J42" s="26"/>
@@ -10416,20 +10030,20 @@
     </row>
     <row r="43" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D43" s="26"/>
       <c r="E43" s="26"/>
       <c r="F43" s="26"/>
       <c r="G43" s="26"/>
       <c r="H43" s="26" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I43" s="26"/>
       <c r="J43" s="26"/>
@@ -10460,10 +10074,10 @@
         <v>90</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="26"/>
@@ -10496,13 +10110,13 @@
     </row>
     <row r="45" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="25" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D45" s="29"/>
       <c r="E45" s="26"/>
@@ -10535,13 +10149,13 @@
     </row>
     <row r="46" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D46" s="25"/>
       <c r="E46" s="26"/>
@@ -10574,13 +10188,13 @@
     </row>
     <row r="47" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D47" s="25"/>
       <c r="E47" s="26"/>
@@ -10613,13 +10227,13 @@
     </row>
     <row r="48" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="25" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D48" s="25"/>
       <c r="E48" s="26"/>
@@ -10652,20 +10266,20 @@
     </row>
     <row r="49" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="25" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D49" s="26"/>
       <c r="E49" s="26"/>
       <c r="F49" s="26"/>
       <c r="G49" s="26"/>
       <c r="H49" s="26" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="I49" s="26"/>
       <c r="J49" s="26"/>
@@ -10693,13 +10307,13 @@
     </row>
     <row r="50" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D50" s="25"/>
       <c r="E50" s="26"/>
@@ -10732,20 +10346,20 @@
     </row>
     <row r="51" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D51" s="26"/>
       <c r="E51" s="26"/>
       <c r="F51" s="26"/>
       <c r="G51" s="26"/>
       <c r="H51" s="26" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="I51" s="26"/>
       <c r="J51" s="26"/>
@@ -10773,13 +10387,13 @@
     </row>
     <row r="52" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D52" s="26"/>
       <c r="E52" s="26"/>
@@ -10815,10 +10429,10 @@
         <v>97</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D53" s="26"/>
       <c r="E53" s="26"/>
@@ -10854,17 +10468,17 @@
         <v>97</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D54" s="26"/>
       <c r="E54" s="26"/>
       <c r="F54" s="26"/>
       <c r="G54" s="26"/>
       <c r="H54" s="26" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="I54" s="26"/>
       <c r="J54" s="26"/>
@@ -10895,17 +10509,17 @@
         <v>97</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D55" s="26"/>
       <c r="E55" s="26"/>
       <c r="F55" s="26"/>
       <c r="G55" s="26"/>
       <c r="H55" s="26" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="I55" s="26"/>
       <c r="J55" s="26"/>
@@ -10936,17 +10550,17 @@
         <v>97</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D56" s="26"/>
       <c r="E56" s="26"/>
       <c r="F56" s="26"/>
       <c r="G56" s="26"/>
       <c r="H56" s="26" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="I56" s="26"/>
       <c r="J56" s="26"/>
@@ -10974,13 +10588,13 @@
     </row>
     <row r="57" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D57" s="26"/>
       <c r="E57" s="26"/>
@@ -11013,13 +10627,13 @@
     </row>
     <row r="58" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D58" s="26"/>
       <c r="E58" s="26"/>
@@ -11052,13 +10666,13 @@
     </row>
     <row r="59" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="25" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -11094,10 +10708,10 @@
         <v>22</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D60" s="26"/>
       <c r="E60" s="26"/>
@@ -11133,7 +10747,7 @@
         <v>26</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C61" s="27"/>
       <c r="D61" s="26"/>
@@ -11170,7 +10784,7 @@
         <v>28</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C62" s="27"/>
       <c r="D62" s="26"/>
@@ -11207,7 +10821,7 @@
         <v>30</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C63" s="27"/>
       <c r="D63" s="26"/>
@@ -11241,10 +10855,10 @@
     </row>
     <row r="64" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="25" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C64" s="27"/>
       <c r="D64" s="26"/>
@@ -11278,10 +10892,10 @@
     </row>
     <row r="65" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="25" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C65" s="27"/>
       <c r="D65" s="26"/>
@@ -11318,7 +10932,7 @@
         <v>39</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C66" s="27"/>
       <c r="D66" s="26"/>
@@ -11355,7 +10969,7 @@
         <v>31</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C67" s="27"/>
       <c r="D67" s="26"/>
@@ -11389,10 +11003,10 @@
     </row>
     <row r="68" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="25" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C68" s="27"/>
       <c r="D68" s="26"/>
@@ -11429,7 +11043,7 @@
         <v>34</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C69" s="27"/>
       <c r="D69" s="26"/>
@@ -11447,7 +11061,7 @@
       <c r="P69" s="26"/>
       <c r="Q69" s="26"/>
       <c r="R69" s="26" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="S69" s="26"/>
       <c r="T69" s="26"/>
@@ -11465,10 +11079,10 @@
     </row>
     <row r="70" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="25" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C70" s="27"/>
       <c r="D70" s="26"/>
@@ -11486,7 +11100,7 @@
       <c r="P70" s="26"/>
       <c r="Q70" s="26"/>
       <c r="R70" s="26" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="S70" s="26"/>
       <c r="T70" s="26"/>
@@ -11504,10 +11118,10 @@
     </row>
     <row r="71" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="25" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C71" s="27"/>
       <c r="D71" s="26"/>
@@ -11515,7 +11129,7 @@
       <c r="F71" s="26"/>
       <c r="G71" s="26"/>
       <c r="H71" s="26" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="I71" s="26"/>
       <c r="J71" s="26"/>
@@ -11543,10 +11157,10 @@
     </row>
     <row r="72" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="26" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C72" s="27"/>
       <c r="D72" s="26"/>
@@ -11554,7 +11168,7 @@
       <c r="F72" s="26"/>
       <c r="G72" s="26"/>
       <c r="H72" s="26" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="I72" s="26"/>
       <c r="J72" s="26"/>
@@ -11582,10 +11196,10 @@
     </row>
     <row r="73" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="25" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C73" s="27"/>
       <c r="D73" s="26"/>
@@ -11593,7 +11207,7 @@
       <c r="F73" s="26"/>
       <c r="G73" s="26"/>
       <c r="H73" s="26" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="I73" s="26"/>
       <c r="J73" s="26"/>
@@ -11621,10 +11235,10 @@
     </row>
     <row r="74" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="25" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C74" s="27"/>
       <c r="D74" s="26"/>
@@ -11632,7 +11246,7 @@
       <c r="F74" s="26"/>
       <c r="G74" s="26"/>
       <c r="H74" s="26" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="I74" s="26"/>
       <c r="J74" s="26"/>
@@ -11660,10 +11274,10 @@
     </row>
     <row r="75" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="25" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C75" s="27"/>
       <c r="D75" s="26"/>
@@ -11671,7 +11285,7 @@
       <c r="F75" s="26"/>
       <c r="G75" s="26"/>
       <c r="H75" s="26" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I75" s="26"/>
       <c r="J75" s="26"/>
@@ -11699,13 +11313,13 @@
     </row>
     <row r="76" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="25" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C76" s="27" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="26"/>
@@ -11738,7 +11352,7 @@
     </row>
     <row r="77" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="26" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B77" s="26"/>
       <c r="C77" s="27"/>
@@ -11773,10 +11387,10 @@
     </row>
     <row r="78" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="26" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C78" s="27"/>
       <c r="D78" s="26"/>
@@ -11810,13 +11424,13 @@
     </row>
     <row r="79" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="25" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D79" s="26"/>
       <c r="E79" s="26"/>
@@ -11849,7 +11463,7 @@
     </row>
     <row r="80" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="26" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="27"/>
@@ -11884,10 +11498,10 @@
     </row>
     <row r="81" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="26" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C81" s="27"/>
       <c r="D81" s="26"/>
@@ -11921,13 +11535,13 @@
     </row>
     <row r="82" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="C82" s="27" t="s">
         <v>405</v>
-      </c>
-      <c r="B82" s="26" t="s">
-        <v>406</v>
-      </c>
-      <c r="C82" s="27" t="s">
-        <v>409</v>
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="26"/>
@@ -11962,7 +11576,7 @@
     </row>
     <row r="83" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="26" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B83" s="26"/>
       <c r="C83" s="27"/>
@@ -11997,10 +11611,10 @@
     </row>
     <row r="84" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C84" s="27"/>
       <c r="D84" s="26"/>
@@ -12034,10 +11648,10 @@
     </row>
     <row r="85" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="25" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C85" s="27"/>
       <c r="D85" s="26"/>
@@ -12071,10 +11685,10 @@
     </row>
     <row r="86" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="25" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C86" s="27"/>
       <c r="D86" s="26"/>
@@ -12108,10 +11722,10 @@
     </row>
     <row r="87" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="25" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C87" s="27"/>
       <c r="D87" s="26"/>
@@ -12119,7 +11733,7 @@
       <c r="F87" s="26"/>
       <c r="G87" s="26"/>
       <c r="H87" s="26" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="I87" s="26"/>
       <c r="J87" s="26"/>
@@ -12147,10 +11761,10 @@
     </row>
     <row r="88" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="25" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C88" s="27"/>
       <c r="D88" s="26"/>
@@ -12158,7 +11772,7 @@
       <c r="F88" s="26"/>
       <c r="G88" s="26"/>
       <c r="H88" s="26" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="I88" s="26"/>
       <c r="J88" s="26"/>
@@ -12186,10 +11800,10 @@
     </row>
     <row r="89" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C89" s="27"/>
       <c r="D89" s="26"/>
@@ -12197,7 +11811,7 @@
       <c r="F89" s="26"/>
       <c r="G89" s="26"/>
       <c r="H89" s="26" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="I89" s="26"/>
       <c r="J89" s="26"/>
@@ -12227,10 +11841,10 @@
       <c r="C90" s="10"/>
     </row>
     <row r="91" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="72" t="s">
-        <v>418</v>
-      </c>
-      <c r="B91" s="68"/>
+      <c r="A91" s="73" t="s">
+        <v>414</v>
+      </c>
+      <c r="B91" s="69"/>
       <c r="C91" s="31"/>
       <c r="D91" s="32"/>
       <c r="E91" s="2"/>
@@ -12262,11 +11876,11 @@
       <c r="AE91" s="2"/>
     </row>
     <row r="92" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="66" t="s">
-        <v>419</v>
-      </c>
-      <c r="B92" s="67"/>
-      <c r="C92" s="68"/>
+      <c r="A92" s="67" t="s">
+        <v>415</v>
+      </c>
+      <c r="B92" s="68"/>
+      <c r="C92" s="69"/>
       <c r="D92" s="32"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
@@ -12301,27 +11915,27 @@
     </row>
     <row r="94" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="33" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C94" s="33" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D94" s="33" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="95" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="34" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B95" s="34" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D95" s="34">
         <v>2</v>
@@ -12329,10 +11943,10 @@
     </row>
     <row r="96" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="34" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B96" s="34" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C96" s="35" t="str">
         <f>"3 - 2"</f>
@@ -12344,13 +11958,13 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="34" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B97" s="34" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D97" s="34">
         <v>6</v>
@@ -12358,13 +11972,13 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="34" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B98" s="34" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D98" s="34">
         <v>5</v>
@@ -12372,13 +11986,13 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="34" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B99" s="34" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D99" s="34">
         <v>1</v>
@@ -12386,128 +12000,128 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="34" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B100" s="34" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D100" s="34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="34" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B101" s="34" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D101" s="34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="34" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B102" s="34" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D102" s="34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="34" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B103" s="34" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D103" s="34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="34" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B104" s="34" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D104" s="34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="34" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B105" s="34" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D105" s="34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="34" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B106" s="34" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D106" s="34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="34" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B107" s="34" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="34" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B108" s="34" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12519,270 +12133,270 @@
     <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="36"/>
       <c r="B110" s="33" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C110" s="33" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D110" s="36"/>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="36"/>
       <c r="B111" s="34" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D111" s="36"/>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="36"/>
       <c r="B112" s="34" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D112" s="36"/>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="36"/>
       <c r="B113" s="39" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C113" s="40" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D113" s="36"/>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="36"/>
       <c r="B114" s="40" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C114" s="40" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D114" s="36"/>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="36"/>
       <c r="B115" s="40" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C115" s="40" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D115" s="36"/>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="36"/>
       <c r="B116" s="40" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C116" s="40" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D116" s="36"/>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="36"/>
       <c r="B117" s="40" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C117" s="40" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D117" s="36"/>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="36"/>
       <c r="B118" s="40" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C118" s="40" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="D118" s="36"/>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="36"/>
       <c r="B119" s="40" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C119" s="40" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D119" s="36"/>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="36"/>
       <c r="B120" s="40" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C120" s="40" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D120" s="36"/>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="36"/>
       <c r="B121" s="40" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C121" s="40" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D121" s="36"/>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="36"/>
       <c r="B122" s="40" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C122" s="40" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D122" s="36"/>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="36"/>
       <c r="B123" s="40" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C123" s="40" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D123" s="36"/>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="36"/>
       <c r="B124" s="40" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C124" s="40" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D124" s="36"/>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="36"/>
       <c r="B125" s="40" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C125" s="40" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D125" s="36"/>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="36"/>
       <c r="B126" s="40" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C126" s="40" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D126" s="36"/>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="36"/>
       <c r="B127" s="40" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C127" s="40" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D127" s="36"/>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="36"/>
       <c r="B128" s="40" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C128" s="40" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D128" s="36"/>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="36"/>
       <c r="B129" s="40" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C129" s="40" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="D129" s="36"/>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="36"/>
       <c r="B130" s="40" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C130" s="40" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D130" s="36"/>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="36"/>
       <c r="B131" s="40" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C131" s="40" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D131" s="36"/>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="36"/>
       <c r="B132" s="40" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C132" s="40" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D132" s="36"/>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="36"/>
       <c r="B133" s="40" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C133" s="40" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D133" s="36"/>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="36"/>
       <c r="B134" s="41" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C134" s="41" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D134" s="36"/>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="36"/>
       <c r="B135" s="41" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C135" s="41" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D135" s="36"/>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="36"/>
       <c r="B136" s="41" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C136" s="41" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D136" s="36"/>
     </row>
@@ -12799,70 +12413,70 @@
     <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="36"/>
       <c r="B138" s="41" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C138" s="41" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D138" s="36"/>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="36"/>
       <c r="B139" s="41" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C139" s="41" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D139" s="36"/>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="36"/>
       <c r="B140" s="41" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C140" s="41" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D140" s="36"/>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="36"/>
       <c r="B141" s="41" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C141" s="41" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D141" s="36"/>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="36"/>
       <c r="B142" s="41" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C142" s="41" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D142" s="36"/>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="36"/>
       <c r="B143" s="41" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C143" s="41" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D143" s="36"/>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="42"/>
       <c r="B144" s="43" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C144" s="43" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D144" s="42"/>
     </row>
@@ -15509,150 +15123,150 @@
     <mergeCell ref="A91:B91"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:AD6">
-    <cfRule type="expression" dxfId="80" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="15" stopIfTrue="1">
       <formula>$A6="comments"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="16" stopIfTrue="1">
       <formula>OR($A6="audio", $A6="video")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="17" stopIfTrue="1">
       <formula>$A6="image"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="18" stopIfTrue="1">
       <formula>OR($A6="date", $A6="datetime")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="19" stopIfTrue="1">
       <formula>OR($A6="calculate", $A6="calculate_here")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="20" stopIfTrue="1">
       <formula>$A6="note"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="21" stopIfTrue="1">
       <formula>$A6="barcode"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="22" stopIfTrue="1">
       <formula>$A6="geopoint"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="23" stopIfTrue="1">
       <formula>OR($A6="audio audit", $A6="text audit")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="24" stopIfTrue="1">
       <formula>OR($A6="phonenumber", $A6="start", $A6="end", $A6="deviceid", $A6="subscriberid", $A6="simserial")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="25" stopIfTrue="1">
       <formula>OR(AND(LEFT($A6, 16)="select_multiple ", LEN($A6)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A6, 17)))), AND(LEFT($A6, 11)="select_one ", LEN($A6)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A6, 12)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="26" stopIfTrue="1">
       <formula>$A6="decimal"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="27" stopIfTrue="1">
       <formula>$A6="integer"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="28" stopIfTrue="1">
       <formula>$A6="text"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="29" stopIfTrue="1">
       <formula>$A6="end repeat"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="30" stopIfTrue="1">
       <formula>$A6="begin repeat"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="31" stopIfTrue="1">
       <formula>$A6="end group"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="32" stopIfTrue="1">
       <formula>$A6="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6 H6">
-    <cfRule type="expression" dxfId="62" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="7" stopIfTrue="1">
       <formula>OR($A6="audio audit", $A6="text audit")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6 R6">
-    <cfRule type="expression" dxfId="61" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="11" stopIfTrue="1">
       <formula>OR($A6="calculate", $A6="calculate_here")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="60" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="33" stopIfTrue="1">
       <formula>$A6="comments"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6 H6 L6">
-    <cfRule type="expression" dxfId="59" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="1" stopIfTrue="1">
       <formula>$A6="begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6 H6">
-    <cfRule type="expression" dxfId="58" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="6" stopIfTrue="1">
       <formula>OR(AND(LEFT($A6, 16)="select_multiple ", LEN($A6)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A6, 17)))), AND(LEFT($A6, 11)="select_one ", LEN($A6)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A6, 12)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="12" stopIfTrue="1">
       <formula>OR($A6="date", $A6="datetime")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="13" stopIfTrue="1">
       <formula>$A6="image"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6 L6 S6">
-    <cfRule type="expression" dxfId="55" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="2" stopIfTrue="1">
       <formula>$A6="begin repeat"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="expression" dxfId="54" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="8" stopIfTrue="1">
       <formula>$A6="note"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="9" stopIfTrue="1">
       <formula>$A6="barcode"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="10" stopIfTrue="1">
       <formula>$A6="geopoint"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="14" stopIfTrue="1">
       <formula>OR($A6="audio", $A6="video")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:F6 H6">
-    <cfRule type="expression" dxfId="50" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="3" stopIfTrue="1">
       <formula>$A6="text"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:F6 I6:K6">
-    <cfRule type="expression" dxfId="49" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="4" stopIfTrue="1">
       <formula>$A6="integer"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="5" stopIfTrue="1">
       <formula>$A6="decimal"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="47" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="52" stopIfTrue="1">
       <formula>$A6="begin group"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="53" stopIfTrue="1">
       <formula>$A6="begin repeat"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="54" stopIfTrue="1">
       <formula>OR(AND(LEFT($A6, 16)="select_multiple ", LEN($A6)&gt;16, NOT(ISNUMBER(SEARCH(" ", $A6, 17)))), AND(LEFT($A6, 11)="select_one ", LEN($A6)&gt;11, NOT(ISNUMBER(SEARCH(" ", $A6, 12)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="55" stopIfTrue="1">
       <formula>$A6="note"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="56" stopIfTrue="1">
       <formula>$A6="barcode"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="57" stopIfTrue="1">
       <formula>$A6="geopoint"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="58" stopIfTrue="1">
       <formula>OR($A6="date", $A6="datetime")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="59" stopIfTrue="1">
       <formula>$A6="image"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="60" stopIfTrue="1">
       <formula>OR($A6="audio", $A6="video")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15725,10 +15339,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
-        <v>528</v>
-      </c>
-      <c r="B1" s="70"/>
+      <c r="A1" s="70" t="s">
+        <v>524</v>
+      </c>
+      <c r="B1" s="71"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -15783,10 +15397,10 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="71" t="s">
-        <v>529</v>
-      </c>
-      <c r="B3" s="63"/>
+      <c r="A3" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="B3" s="64"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -15813,10 +15427,10 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="B4" s="63"/>
+      <c r="A4" s="74" t="s">
+        <v>526</v>
+      </c>
+      <c r="B4" s="64"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -15843,10 +15457,10 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="73" t="s">
-        <v>531</v>
-      </c>
-      <c r="B5" s="63"/>
+      <c r="A5" s="74" t="s">
+        <v>527</v>
+      </c>
+      <c r="B5" s="64"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -15873,10 +15487,10 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="60" t="s">
-        <v>532</v>
-      </c>
-      <c r="B6" s="61"/>
+      <c r="A6" s="61" t="s">
+        <v>528</v>
+      </c>
+      <c r="B6" s="62"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -15938,16 +15552,16 @@
         <v>96</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>97</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>98</v>
@@ -15974,25 +15588,25 @@
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="48" t="s">
+        <v>530</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>531</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>532</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>258</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>533</v>
+      </c>
+      <c r="F9" s="48" t="s">
         <v>534</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="G9" s="48" t="s">
         <v>535</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>536</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>262</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>537</v>
-      </c>
-      <c r="F9" s="48" t="s">
-        <v>538</v>
-      </c>
-      <c r="G9" s="48" t="s">
-        <v>539</v>
       </c>
       <c r="H9" s="48"/>
       <c r="I9" s="49"/>
@@ -16019,14 +15633,14 @@
       <c r="B10" s="50"/>
       <c r="C10" s="50"/>
       <c r="D10" s="51" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F10" s="50"/>
       <c r="G10" s="52" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="H10" s="50"/>
       <c r="I10" s="50"/>
@@ -17066,10 +16680,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
-        <v>540</v>
-      </c>
-      <c r="B1" s="79"/>
+      <c r="A1" s="79" t="s">
+        <v>536</v>
+      </c>
+      <c r="B1" s="80"/>
       <c r="C1" s="53"/>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -17096,8 +16710,8 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="78"/>
       <c r="C2" s="53"/>
       <c r="D2" s="53"/>
       <c r="E2" s="53"/>
@@ -17124,10 +16738,10 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="74" t="s">
-        <v>541</v>
-      </c>
-      <c r="B3" s="75"/>
+      <c r="A3" s="75" t="s">
+        <v>537</v>
+      </c>
+      <c r="B3" s="76"/>
       <c r="C3" s="53"/>
       <c r="D3" s="53"/>
       <c r="E3" s="53"/>
@@ -17183,22 +16797,22 @@
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="F5" s="55" t="s">
         <v>240</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>241</v>
-      </c>
-      <c r="D5" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="E5" s="54" t="s">
-        <v>243</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>244</v>
       </c>
       <c r="G5" s="56"/>
       <c r="H5" s="57"/>
@@ -17223,22 +16837,22 @@
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
+        <v>538</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>539</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>542</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="F6" s="14" t="s">
         <v>543</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>547</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
@@ -17263,20 +16877,20 @@
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B7" s="58"/>
       <c r="C7" s="21" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
